--- a/docs/data/standeskommission.xlsx
+++ b/docs/data/standeskommission.xlsx
@@ -5,16 +5,19 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\docs\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B2562CA-34EC-4383-B703-DB93C4CF5D7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A66EEF8-82D5-4C27-8FF3-D315AB3A359B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23136" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{669C7B45-B26B-4B76-A8C9-B2BF60283C86}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{669C7B45-B26B-4B76-A8C9-B2BF60283C86}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tabelle1!$A$1:$G$1</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1191" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1817" uniqueCount="94">
   <si>
     <t>Jahr</t>
   </si>
@@ -285,6 +288,39 @@
   </si>
   <si>
     <t>Justiz- und Polizeidepartement &amp; Militärdepartement</t>
+  </si>
+  <si>
+    <t>Manser</t>
+  </si>
+  <si>
+    <t>Neff</t>
+  </si>
+  <si>
+    <t>Emil</t>
+  </si>
+  <si>
+    <t>Zeller</t>
+  </si>
+  <si>
+    <t>Breu</t>
+  </si>
+  <si>
+    <t>Albert</t>
+  </si>
+  <si>
+    <t>Reihenfolge</t>
+  </si>
+  <si>
+    <t>Graf</t>
+  </si>
+  <si>
+    <t>Beat</t>
+  </si>
+  <si>
+    <t>Breitenmoser</t>
+  </si>
+  <si>
+    <t>Franz</t>
   </si>
 </sst>
 </file>
@@ -300,12 +336,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -320,8 +362,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -656,18 +699,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FB2D094-259F-4BDA-9CCC-AC85399FAC35}">
-  <dimension ref="A1:F238"/>
+  <dimension ref="A1:G363"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="30.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="41" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -686,8 +729,11 @@
       <c r="F1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2025</v>
       </c>
@@ -706,8 +752,11 @@
       <c r="F2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2025</v>
       </c>
@@ -726,8 +775,11 @@
       <c r="F3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2025</v>
       </c>
@@ -746,8 +798,11 @@
       <c r="F4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2025</v>
       </c>
@@ -766,8 +821,11 @@
       <c r="F5" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2025</v>
       </c>
@@ -786,8 +844,11 @@
       <c r="F6" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2025</v>
       </c>
@@ -806,8 +867,11 @@
       <c r="F7" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2025</v>
       </c>
@@ -826,8 +890,11 @@
       <c r="F8" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2024</v>
       </c>
@@ -846,8 +913,11 @@
       <c r="F9" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2024</v>
       </c>
@@ -866,8 +936,11 @@
       <c r="F10" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2024</v>
       </c>
@@ -886,8 +959,11 @@
       <c r="F11" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2024</v>
       </c>
@@ -906,8 +982,11 @@
       <c r="F12" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2024</v>
       </c>
@@ -926,8 +1005,11 @@
       <c r="F13" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2024</v>
       </c>
@@ -946,8 +1028,11 @@
       <c r="F14" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2024</v>
       </c>
@@ -966,8 +1051,11 @@
       <c r="F15" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2023</v>
       </c>
@@ -986,8 +1074,11 @@
       <c r="F16" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2023</v>
       </c>
@@ -1006,8 +1097,11 @@
       <c r="F17" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2023</v>
       </c>
@@ -1026,8 +1120,11 @@
       <c r="F18" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2023</v>
       </c>
@@ -1046,8 +1143,11 @@
       <c r="F19" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2023</v>
       </c>
@@ -1066,8 +1166,11 @@
       <c r="F20" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2023</v>
       </c>
@@ -1086,8 +1189,11 @@
       <c r="F21" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G21">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2023</v>
       </c>
@@ -1106,8 +1212,11 @@
       <c r="F22" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G22">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2022</v>
       </c>
@@ -1126,8 +1235,11 @@
       <c r="F23" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2022</v>
       </c>
@@ -1146,8 +1258,11 @@
       <c r="F24" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2022</v>
       </c>
@@ -1166,8 +1281,11 @@
       <c r="F25" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2022</v>
       </c>
@@ -1186,8 +1304,11 @@
       <c r="F26" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G26">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2022</v>
       </c>
@@ -1206,8 +1327,11 @@
       <c r="F27" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2022</v>
       </c>
@@ -1226,8 +1350,11 @@
       <c r="F28" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G28">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2022</v>
       </c>
@@ -1246,8 +1373,11 @@
       <c r="F29" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G29">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>2021</v>
       </c>
@@ -1266,8 +1396,11 @@
       <c r="F30" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2021</v>
       </c>
@@ -1286,8 +1419,11 @@
       <c r="F31" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>2021</v>
       </c>
@@ -1306,8 +1442,11 @@
       <c r="F32" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G32">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>2021</v>
       </c>
@@ -1326,8 +1465,11 @@
       <c r="F33" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G33">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>2021</v>
       </c>
@@ -1346,8 +1488,11 @@
       <c r="F34" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G34">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>2021</v>
       </c>
@@ -1366,8 +1511,11 @@
       <c r="F35" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>2021</v>
       </c>
@@ -1386,8 +1534,11 @@
       <c r="F36" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G36">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>2020</v>
       </c>
@@ -1406,8 +1557,11 @@
       <c r="F37" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>2020</v>
       </c>
@@ -1426,8 +1580,11 @@
       <c r="F38" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>2020</v>
       </c>
@@ -1446,8 +1603,11 @@
       <c r="F39" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G39">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>2020</v>
       </c>
@@ -1466,8 +1626,11 @@
       <c r="F40" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G40">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>2020</v>
       </c>
@@ -1486,8 +1649,11 @@
       <c r="F41" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G41">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>2020</v>
       </c>
@@ -1506,8 +1672,11 @@
       <c r="F42" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G42">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>2020</v>
       </c>
@@ -1526,8 +1695,11 @@
       <c r="F43" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G43">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>2019</v>
       </c>
@@ -1546,8 +1718,11 @@
       <c r="F44" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>2019</v>
       </c>
@@ -1566,8 +1741,11 @@
       <c r="F45" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G45">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>2019</v>
       </c>
@@ -1586,8 +1764,11 @@
       <c r="F46" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G46">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>2019</v>
       </c>
@@ -1606,8 +1787,11 @@
       <c r="F47" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G47">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>2019</v>
       </c>
@@ -1626,8 +1810,11 @@
       <c r="F48" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G48">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>2019</v>
       </c>
@@ -1646,8 +1833,11 @@
       <c r="F49" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G49">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>2019</v>
       </c>
@@ -1666,8 +1856,11 @@
       <c r="F50" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G50">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>2018</v>
       </c>
@@ -1686,8 +1879,11 @@
       <c r="F51" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>2018</v>
       </c>
@@ -1706,8 +1902,11 @@
       <c r="F52" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G52">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>2018</v>
       </c>
@@ -1726,8 +1925,11 @@
       <c r="F53" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G53">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>2018</v>
       </c>
@@ -1746,8 +1948,11 @@
       <c r="F54" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G54">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>2018</v>
       </c>
@@ -1766,8 +1971,11 @@
       <c r="F55" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G55">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>2018</v>
       </c>
@@ -1786,8 +1994,11 @@
       <c r="F56" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G56">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>2018</v>
       </c>
@@ -1806,8 +2017,11 @@
       <c r="F57" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G57">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>2017</v>
       </c>
@@ -1826,8 +2040,11 @@
       <c r="F58" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>2017</v>
       </c>
@@ -1846,8 +2063,11 @@
       <c r="F59" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G59">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>2017</v>
       </c>
@@ -1866,8 +2086,11 @@
       <c r="F60" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G60">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>2017</v>
       </c>
@@ -1886,8 +2109,11 @@
       <c r="F61" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G61">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>2017</v>
       </c>
@@ -1906,8 +2132,11 @@
       <c r="F62" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G62">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>2017</v>
       </c>
@@ -1926,8 +2155,11 @@
       <c r="F63" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G63">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>2017</v>
       </c>
@@ -1946,8 +2178,11 @@
       <c r="F64" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G64">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>2016</v>
       </c>
@@ -1966,8 +2201,11 @@
       <c r="F65" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>2016</v>
       </c>
@@ -1986,8 +2224,11 @@
       <c r="F66" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G66">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>2016</v>
       </c>
@@ -2006,8 +2247,11 @@
       <c r="F67" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G67">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>2016</v>
       </c>
@@ -2026,8 +2270,11 @@
       <c r="F68" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G68">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>2016</v>
       </c>
@@ -2046,8 +2293,11 @@
       <c r="F69" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G69">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>2016</v>
       </c>
@@ -2066,8 +2316,11 @@
       <c r="F70" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G70">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>2016</v>
       </c>
@@ -2086,8 +2339,11 @@
       <c r="F71" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G71">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>2015</v>
       </c>
@@ -2106,8 +2362,11 @@
       <c r="F72" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>2015</v>
       </c>
@@ -2126,8 +2385,11 @@
       <c r="F73" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G73">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>2015</v>
       </c>
@@ -2146,8 +2408,11 @@
       <c r="F74" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G74">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>2015</v>
       </c>
@@ -2166,8 +2431,11 @@
       <c r="F75" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G75">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>2015</v>
       </c>
@@ -2186,8 +2454,11 @@
       <c r="F76" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G76">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>2015</v>
       </c>
@@ -2206,8 +2477,11 @@
       <c r="F77" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G77">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>2015</v>
       </c>
@@ -2226,8 +2500,11 @@
       <c r="F78" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G78">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>2014</v>
       </c>
@@ -2246,8 +2523,11 @@
       <c r="F79" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>2014</v>
       </c>
@@ -2266,8 +2546,11 @@
       <c r="F80" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G80">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>2014</v>
       </c>
@@ -2286,8 +2569,11 @@
       <c r="F81" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G81">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>2014</v>
       </c>
@@ -2306,8 +2592,11 @@
       <c r="F82" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G82">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>2014</v>
       </c>
@@ -2326,8 +2615,11 @@
       <c r="F83" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G83">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>2014</v>
       </c>
@@ -2346,8 +2638,11 @@
       <c r="F84" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G84">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>2014</v>
       </c>
@@ -2366,8 +2661,11 @@
       <c r="F85" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G85">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>2013</v>
       </c>
@@ -2386,8 +2684,11 @@
       <c r="F86" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>2013</v>
       </c>
@@ -2406,8 +2707,11 @@
       <c r="F87" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G87">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>2013</v>
       </c>
@@ -2426,8 +2730,11 @@
       <c r="F88" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G88">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>2013</v>
       </c>
@@ -2446,8 +2753,11 @@
       <c r="F89" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G89">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>2013</v>
       </c>
@@ -2466,8 +2776,11 @@
       <c r="F90" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G90">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>2013</v>
       </c>
@@ -2486,8 +2799,11 @@
       <c r="F91" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G91">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>2013</v>
       </c>
@@ -2506,8 +2822,11 @@
       <c r="F92" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G92">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>2012</v>
       </c>
@@ -2526,8 +2845,11 @@
       <c r="F93" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>2012</v>
       </c>
@@ -2546,8 +2868,11 @@
       <c r="F94" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G94">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>2012</v>
       </c>
@@ -2566,8 +2891,11 @@
       <c r="F95" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G95">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>2012</v>
       </c>
@@ -2586,8 +2914,11 @@
       <c r="F96" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G96">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>2012</v>
       </c>
@@ -2606,8 +2937,11 @@
       <c r="F97" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G97">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>2012</v>
       </c>
@@ -2626,8 +2960,11 @@
       <c r="F98" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G98">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>2012</v>
       </c>
@@ -2646,8 +2983,11 @@
       <c r="F99" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G99">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>2011</v>
       </c>
@@ -2666,8 +3006,11 @@
       <c r="F100" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>2011</v>
       </c>
@@ -2686,8 +3029,11 @@
       <c r="F101" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G101">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>2011</v>
       </c>
@@ -2706,8 +3052,11 @@
       <c r="F102" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G102">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>2011</v>
       </c>
@@ -2726,8 +3075,11 @@
       <c r="F103" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G103">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>2011</v>
       </c>
@@ -2746,8 +3098,11 @@
       <c r="F104" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G104">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>2011</v>
       </c>
@@ -2766,8 +3121,11 @@
       <c r="F105" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G105">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>2011</v>
       </c>
@@ -2786,8 +3144,11 @@
       <c r="F106" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G106">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>2010</v>
       </c>
@@ -2806,8 +3167,11 @@
       <c r="F107" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G107">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>2010</v>
       </c>
@@ -2826,8 +3190,11 @@
       <c r="F108" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G108">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>2010</v>
       </c>
@@ -2846,8 +3213,11 @@
       <c r="F109" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G109">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>2010</v>
       </c>
@@ -2866,8 +3236,11 @@
       <c r="F110" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G110">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>2010</v>
       </c>
@@ -2886,8 +3259,11 @@
       <c r="F111" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G111">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>2010</v>
       </c>
@@ -2906,8 +3282,11 @@
       <c r="F112" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G112">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>2010</v>
       </c>
@@ -2926,8 +3305,11 @@
       <c r="F113" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G113">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>2009</v>
       </c>
@@ -2946,8 +3328,11 @@
       <c r="F114" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G114">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>2009</v>
       </c>
@@ -2966,8 +3351,11 @@
       <c r="F115" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G115">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>2009</v>
       </c>
@@ -2986,8 +3374,11 @@
       <c r="F116" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G116">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>2009</v>
       </c>
@@ -3006,8 +3397,11 @@
       <c r="F117" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G117">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>2009</v>
       </c>
@@ -3026,8 +3420,11 @@
       <c r="F118" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G118">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>2009</v>
       </c>
@@ -3046,8 +3443,11 @@
       <c r="F119" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G119">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>2009</v>
       </c>
@@ -3066,8 +3466,11 @@
       <c r="F120" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G120">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>2008</v>
       </c>
@@ -3086,8 +3489,11 @@
       <c r="F121" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>2008</v>
       </c>
@@ -3106,8 +3512,11 @@
       <c r="F122" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G122">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>2008</v>
       </c>
@@ -3126,8 +3535,11 @@
       <c r="F123" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G123">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>2008</v>
       </c>
@@ -3146,8 +3558,11 @@
       <c r="F124" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G124">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>2008</v>
       </c>
@@ -3166,8 +3581,11 @@
       <c r="F125" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G125">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>2008</v>
       </c>
@@ -3186,8 +3604,11 @@
       <c r="F126" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G126">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>2008</v>
       </c>
@@ -3206,8 +3627,11 @@
       <c r="F127" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G127">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>2007</v>
       </c>
@@ -3226,8 +3650,11 @@
       <c r="F128" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G128">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>2007</v>
       </c>
@@ -3246,8 +3673,11 @@
       <c r="F129" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G129">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>2007</v>
       </c>
@@ -3266,8 +3696,11 @@
       <c r="F130" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G130">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>2007</v>
       </c>
@@ -3286,8 +3719,11 @@
       <c r="F131" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G131">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>2007</v>
       </c>
@@ -3306,8 +3742,11 @@
       <c r="F132" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G132">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>2007</v>
       </c>
@@ -3326,8 +3765,11 @@
       <c r="F133" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G133">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>2007</v>
       </c>
@@ -3346,8 +3788,11 @@
       <c r="F134" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G134">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>2006</v>
       </c>
@@ -3366,8 +3811,11 @@
       <c r="F135" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G135">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>2006</v>
       </c>
@@ -3386,8 +3834,11 @@
       <c r="F136" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G136">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>2006</v>
       </c>
@@ -3406,8 +3857,11 @@
       <c r="F137" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G137">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>2006</v>
       </c>
@@ -3426,8 +3880,11 @@
       <c r="F138" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G138">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>2006</v>
       </c>
@@ -3446,8 +3903,11 @@
       <c r="F139" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G139">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>2006</v>
       </c>
@@ -3466,8 +3926,11 @@
       <c r="F140" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G140">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>2006</v>
       </c>
@@ -3486,8 +3949,11 @@
       <c r="F141" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G141">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>2005</v>
       </c>
@@ -3506,8 +3972,11 @@
       <c r="F142" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G142">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>2005</v>
       </c>
@@ -3526,8 +3995,11 @@
       <c r="F143" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G143">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>2005</v>
       </c>
@@ -3546,8 +4018,11 @@
       <c r="F144" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G144">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>2005</v>
       </c>
@@ -3566,8 +4041,11 @@
       <c r="F145" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G145">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>2005</v>
       </c>
@@ -3586,8 +4064,11 @@
       <c r="F146" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G146">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>2005</v>
       </c>
@@ -3606,8 +4087,11 @@
       <c r="F147" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G147">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>2005</v>
       </c>
@@ -3626,8 +4110,11 @@
       <c r="F148" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G148">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>2004</v>
       </c>
@@ -3646,8 +4133,11 @@
       <c r="F149" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>2004</v>
       </c>
@@ -3666,8 +4156,11 @@
       <c r="F150" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G150">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>2004</v>
       </c>
@@ -3686,8 +4179,11 @@
       <c r="F151" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G151">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>2004</v>
       </c>
@@ -3706,8 +4202,11 @@
       <c r="F152" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G152">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>2004</v>
       </c>
@@ -3726,8 +4225,11 @@
       <c r="F153" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G153">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>2004</v>
       </c>
@@ -3746,8 +4248,11 @@
       <c r="F154" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G154">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>2004</v>
       </c>
@@ -3766,8 +4271,11 @@
       <c r="F155" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G155">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>2003</v>
       </c>
@@ -3786,8 +4294,11 @@
       <c r="F156" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G156">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>2003</v>
       </c>
@@ -3806,8 +4317,11 @@
       <c r="F157" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G157">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>2003</v>
       </c>
@@ -3826,8 +4340,11 @@
       <c r="F158" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G158">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>2003</v>
       </c>
@@ -3846,8 +4363,11 @@
       <c r="F159" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G159">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>2003</v>
       </c>
@@ -3866,8 +4386,11 @@
       <c r="F160" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G160">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>2003</v>
       </c>
@@ -3886,8 +4409,11 @@
       <c r="F161" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G161">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>2003</v>
       </c>
@@ -3906,8 +4432,11 @@
       <c r="F162" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G162">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>2002</v>
       </c>
@@ -3926,8 +4455,11 @@
       <c r="F163" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G163">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>2002</v>
       </c>
@@ -3946,8 +4478,11 @@
       <c r="F164" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G164">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>2002</v>
       </c>
@@ -3966,8 +4501,11 @@
       <c r="F165" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G165">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>2002</v>
       </c>
@@ -3986,8 +4524,11 @@
       <c r="F166" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G166">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>2002</v>
       </c>
@@ -4006,8 +4547,11 @@
       <c r="F167" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G167">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>2002</v>
       </c>
@@ -4026,8 +4570,11 @@
       <c r="F168" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G168">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>2002</v>
       </c>
@@ -4046,8 +4593,11 @@
       <c r="F169" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G169">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>2001</v>
       </c>
@@ -4066,8 +4616,11 @@
       <c r="F170" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G170">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>2001</v>
       </c>
@@ -4086,8 +4639,11 @@
       <c r="F171" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G171">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>2001</v>
       </c>
@@ -4106,8 +4662,11 @@
       <c r="F172" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G172">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>2001</v>
       </c>
@@ -4126,8 +4685,11 @@
       <c r="F173" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G173">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>2001</v>
       </c>
@@ -4146,8 +4708,11 @@
       <c r="F174" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G174">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>2001</v>
       </c>
@@ -4166,8 +4731,11 @@
       <c r="F175" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G175">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>2001</v>
       </c>
@@ -4186,8 +4754,11 @@
       <c r="F176" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G176">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>2000</v>
       </c>
@@ -4206,8 +4777,11 @@
       <c r="F177" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G177">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>2000</v>
       </c>
@@ -4226,8 +4800,11 @@
       <c r="F178" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G178">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>2000</v>
       </c>
@@ -4246,8 +4823,11 @@
       <c r="F179" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G179">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>2000</v>
       </c>
@@ -4266,8 +4846,11 @@
       <c r="F180" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G180">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>2000</v>
       </c>
@@ -4286,8 +4869,11 @@
       <c r="F181" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G181">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>2000</v>
       </c>
@@ -4306,8 +4892,11 @@
       <c r="F182" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G182">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>2000</v>
       </c>
@@ -4326,8 +4915,11 @@
       <c r="F183" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G183">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>1999</v>
       </c>
@@ -4346,8 +4938,11 @@
       <c r="F184" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G184">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>1999</v>
       </c>
@@ -4366,8 +4961,11 @@
       <c r="F185" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G185">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>1999</v>
       </c>
@@ -4386,8 +4984,11 @@
       <c r="F186" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G186">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>1999</v>
       </c>
@@ -4406,8 +5007,11 @@
       <c r="F187" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G187">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>1999</v>
       </c>
@@ -4426,8 +5030,11 @@
       <c r="F188" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G188">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>1999</v>
       </c>
@@ -4446,8 +5053,11 @@
       <c r="F189" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G189">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>1999</v>
       </c>
@@ -4466,8 +5076,11 @@
       <c r="F190" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G190">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>1998</v>
       </c>
@@ -4486,8 +5099,11 @@
       <c r="F191" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G191">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>1998</v>
       </c>
@@ -4506,8 +5122,11 @@
       <c r="F192" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G192">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>1998</v>
       </c>
@@ -4526,8 +5145,11 @@
       <c r="F193" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G193">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>1998</v>
       </c>
@@ -4546,8 +5168,11 @@
       <c r="F194" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G194">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>1998</v>
       </c>
@@ -4566,8 +5191,11 @@
       <c r="F195" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G195">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>1998</v>
       </c>
@@ -4586,8 +5214,11 @@
       <c r="F196" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G196">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>1998</v>
       </c>
@@ -4606,8 +5237,11 @@
       <c r="F197" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G197">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>1997</v>
       </c>
@@ -4626,8 +5260,11 @@
       <c r="F198" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G198">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>1997</v>
       </c>
@@ -4646,8 +5283,11 @@
       <c r="F199" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G199">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>1997</v>
       </c>
@@ -4666,8 +5306,11 @@
       <c r="F200" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G200">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>1997</v>
       </c>
@@ -4686,8 +5329,11 @@
       <c r="F201" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G201">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>1997</v>
       </c>
@@ -4706,8 +5352,11 @@
       <c r="F202" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G202">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>1997</v>
       </c>
@@ -4726,8 +5375,11 @@
       <c r="F203" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G203">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>1997</v>
       </c>
@@ -4746,8 +5398,11 @@
       <c r="F204" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G204">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>1996</v>
       </c>
@@ -4766,8 +5421,11 @@
       <c r="F205" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G205">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>1996</v>
       </c>
@@ -4786,8 +5444,11 @@
       <c r="F206" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G206">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>1996</v>
       </c>
@@ -4806,8 +5467,11 @@
       <c r="F207" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G207">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>1996</v>
       </c>
@@ -4826,8 +5490,11 @@
       <c r="F208" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G208">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>1996</v>
       </c>
@@ -4846,8 +5513,11 @@
       <c r="F209" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G209">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>1996</v>
       </c>
@@ -4866,8 +5536,11 @@
       <c r="F210" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G210">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>1996</v>
       </c>
@@ -4886,8 +5559,11 @@
       <c r="F211" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G211">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>1995</v>
       </c>
@@ -4906,8 +5582,11 @@
       <c r="F212" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G212">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>1995</v>
       </c>
@@ -4926,8 +5605,11 @@
       <c r="F213" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G213">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>1995</v>
       </c>
@@ -4946,8 +5628,11 @@
       <c r="F214" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G214">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>1995</v>
       </c>
@@ -4966,8 +5651,11 @@
       <c r="F215" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G215">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>1995</v>
       </c>
@@ -4986,8 +5674,11 @@
       <c r="F216" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G216">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>1995</v>
       </c>
@@ -5006,8 +5697,11 @@
       <c r="F217" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G217">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>1995</v>
       </c>
@@ -5026,8 +5720,11 @@
       <c r="F218" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G218">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>1995</v>
       </c>
@@ -5046,8 +5743,11 @@
       <c r="F219" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G219">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>1995</v>
       </c>
@@ -5066,8 +5766,11 @@
       <c r="F220" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G220">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>1994</v>
       </c>
@@ -5086,8 +5789,11 @@
       <c r="F221" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G221">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>1994</v>
       </c>
@@ -5106,8 +5812,11 @@
       <c r="F222" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G222">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>1994</v>
       </c>
@@ -5126,8 +5835,11 @@
       <c r="F223" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G223">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>1994</v>
       </c>
@@ -5146,8 +5858,11 @@
       <c r="F224" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G224">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>1994</v>
       </c>
@@ -5166,8 +5881,11 @@
       <c r="F225" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G225">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>1994</v>
       </c>
@@ -5186,8 +5904,11 @@
       <c r="F226" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G226">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>1994</v>
       </c>
@@ -5206,8 +5927,11 @@
       <c r="F227" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G227">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>1994</v>
       </c>
@@ -5226,8 +5950,11 @@
       <c r="F228" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G228">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>1994</v>
       </c>
@@ -5246,8 +5973,11 @@
       <c r="F229" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G229">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>1993</v>
       </c>
@@ -5266,8 +5996,11 @@
       <c r="F230" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G230">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>1993</v>
       </c>
@@ -5286,8 +6019,11 @@
       <c r="F231" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G231">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>1993</v>
       </c>
@@ -5306,8 +6042,11 @@
       <c r="F232" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G232">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>1993</v>
       </c>
@@ -5326,8 +6065,11 @@
       <c r="F233" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G233">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>1993</v>
       </c>
@@ -5346,8 +6088,11 @@
       <c r="F234" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G234">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>1993</v>
       </c>
@@ -5366,8 +6111,11 @@
       <c r="F235" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G235">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>1993</v>
       </c>
@@ -5386,8 +6134,11 @@
       <c r="F236" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G236">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>1993</v>
       </c>
@@ -5406,8 +6157,11 @@
       <c r="F237" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G237">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>1993</v>
       </c>
@@ -5426,8 +6180,2891 @@
       <c r="F238" t="s">
         <v>78</v>
       </c>
+      <c r="G238">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A239">
+        <v>1992</v>
+      </c>
+      <c r="B239" t="s">
+        <v>90</v>
+      </c>
+      <c r="C239" t="s">
+        <v>91</v>
+      </c>
+      <c r="D239" t="s">
+        <v>35</v>
+      </c>
+      <c r="E239" t="s">
+        <v>37</v>
+      </c>
+      <c r="F239" t="s">
+        <v>10</v>
+      </c>
+      <c r="G239">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A240">
+        <v>1992</v>
+      </c>
+      <c r="B240" t="s">
+        <v>48</v>
+      </c>
+      <c r="C240" t="s">
+        <v>49</v>
+      </c>
+      <c r="D240" t="s">
+        <v>35</v>
+      </c>
+      <c r="E240" t="s">
+        <v>9</v>
+      </c>
+      <c r="F240" t="s">
+        <v>22</v>
+      </c>
+      <c r="G240">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A241">
+        <v>1992</v>
+      </c>
+      <c r="B241" t="s">
+        <v>63</v>
+      </c>
+      <c r="C241" t="s">
+        <v>32</v>
+      </c>
+      <c r="D241" t="s">
+        <v>35</v>
+      </c>
+      <c r="E241" t="s">
+        <v>56</v>
+      </c>
+      <c r="F241" t="s">
+        <v>79</v>
+      </c>
+      <c r="G241">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A242">
+        <v>1992</v>
+      </c>
+      <c r="B242" t="s">
+        <v>39</v>
+      </c>
+      <c r="C242" t="s">
+        <v>70</v>
+      </c>
+      <c r="D242" t="s">
+        <v>35</v>
+      </c>
+      <c r="E242" t="s">
+        <v>13</v>
+      </c>
+      <c r="F242" t="s">
+        <v>14</v>
+      </c>
+      <c r="G242">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A243">
+        <v>1992</v>
+      </c>
+      <c r="B243" t="s">
+        <v>36</v>
+      </c>
+      <c r="C243" t="s">
+        <v>64</v>
+      </c>
+      <c r="D243" t="s">
+        <v>35</v>
+      </c>
+      <c r="E243" t="s">
+        <v>15</v>
+      </c>
+      <c r="F243" t="s">
+        <v>16</v>
+      </c>
+      <c r="G243">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A244">
+        <v>1992</v>
+      </c>
+      <c r="B244" t="s">
+        <v>46</v>
+      </c>
+      <c r="C244" t="s">
+        <v>32</v>
+      </c>
+      <c r="D244" t="s">
+        <v>35</v>
+      </c>
+      <c r="E244" t="s">
+        <v>17</v>
+      </c>
+      <c r="F244" t="s">
+        <v>75</v>
+      </c>
+      <c r="G244">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A245">
+        <v>1992</v>
+      </c>
+      <c r="B245" t="s">
+        <v>61</v>
+      </c>
+      <c r="C245" t="s">
+        <v>62</v>
+      </c>
+      <c r="D245" t="s">
+        <v>35</v>
+      </c>
+      <c r="E245" t="s">
+        <v>19</v>
+      </c>
+      <c r="F245" t="s">
+        <v>77</v>
+      </c>
+      <c r="G245">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A246">
+        <v>1992</v>
+      </c>
+      <c r="B246" t="s">
+        <v>46</v>
+      </c>
+      <c r="C246" t="s">
+        <v>64</v>
+      </c>
+      <c r="D246" t="s">
+        <v>35</v>
+      </c>
+      <c r="E246" t="s">
+        <v>71</v>
+      </c>
+      <c r="F246" t="s">
+        <v>76</v>
+      </c>
+      <c r="G246">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A247">
+        <v>1992</v>
+      </c>
+      <c r="B247" t="s">
+        <v>72</v>
+      </c>
+      <c r="C247" t="s">
+        <v>73</v>
+      </c>
+      <c r="D247" t="s">
+        <v>35</v>
+      </c>
+      <c r="E247" t="s">
+        <v>74</v>
+      </c>
+      <c r="F247" t="s">
+        <v>78</v>
+      </c>
+      <c r="G247">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A248">
+        <v>1991</v>
+      </c>
+      <c r="B248" t="s">
+        <v>90</v>
+      </c>
+      <c r="C248" t="s">
+        <v>91</v>
+      </c>
+      <c r="D248" t="s">
+        <v>35</v>
+      </c>
+      <c r="E248" t="s">
+        <v>9</v>
+      </c>
+      <c r="F248" t="s">
+        <v>10</v>
+      </c>
+      <c r="G248">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A249">
+        <v>1991</v>
+      </c>
+      <c r="B249" t="s">
+        <v>48</v>
+      </c>
+      <c r="C249" t="s">
+        <v>49</v>
+      </c>
+      <c r="D249" t="s">
+        <v>35</v>
+      </c>
+      <c r="E249" t="s">
+        <v>37</v>
+      </c>
+      <c r="F249" t="s">
+        <v>22</v>
+      </c>
+      <c r="G249">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A250">
+        <v>1991</v>
+      </c>
+      <c r="B250" t="s">
+        <v>83</v>
+      </c>
+      <c r="C250" t="s">
+        <v>32</v>
+      </c>
+      <c r="D250" t="s">
+        <v>35</v>
+      </c>
+      <c r="E250" t="s">
+        <v>56</v>
+      </c>
+      <c r="F250" t="s">
+        <v>79</v>
+      </c>
+      <c r="G250">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A251">
+        <v>1991</v>
+      </c>
+      <c r="B251" t="s">
+        <v>39</v>
+      </c>
+      <c r="C251" t="s">
+        <v>70</v>
+      </c>
+      <c r="D251" t="s">
+        <v>35</v>
+      </c>
+      <c r="E251" t="s">
+        <v>13</v>
+      </c>
+      <c r="F251" t="s">
+        <v>14</v>
+      </c>
+      <c r="G251">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A252">
+        <v>1991</v>
+      </c>
+      <c r="B252" t="s">
+        <v>36</v>
+      </c>
+      <c r="C252" t="s">
+        <v>64</v>
+      </c>
+      <c r="D252" t="s">
+        <v>35</v>
+      </c>
+      <c r="E252" t="s">
+        <v>15</v>
+      </c>
+      <c r="F252" t="s">
+        <v>16</v>
+      </c>
+      <c r="G252">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A253">
+        <v>1991</v>
+      </c>
+      <c r="B253" t="s">
+        <v>84</v>
+      </c>
+      <c r="C253" t="s">
+        <v>85</v>
+      </c>
+      <c r="D253" t="s">
+        <v>35</v>
+      </c>
+      <c r="E253" t="s">
+        <v>17</v>
+      </c>
+      <c r="F253" t="s">
+        <v>75</v>
+      </c>
+      <c r="G253">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A254">
+        <v>1991</v>
+      </c>
+      <c r="B254" t="s">
+        <v>61</v>
+      </c>
+      <c r="C254" t="s">
+        <v>62</v>
+      </c>
+      <c r="D254" t="s">
+        <v>35</v>
+      </c>
+      <c r="E254" t="s">
+        <v>19</v>
+      </c>
+      <c r="F254" t="s">
+        <v>77</v>
+      </c>
+      <c r="G254">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A255">
+        <v>1991</v>
+      </c>
+      <c r="B255" t="s">
+        <v>46</v>
+      </c>
+      <c r="C255" t="s">
+        <v>64</v>
+      </c>
+      <c r="D255" t="s">
+        <v>35</v>
+      </c>
+      <c r="E255" t="s">
+        <v>71</v>
+      </c>
+      <c r="F255" t="s">
+        <v>76</v>
+      </c>
+      <c r="G255">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A256">
+        <v>1991</v>
+      </c>
+      <c r="B256" t="s">
+        <v>72</v>
+      </c>
+      <c r="C256" t="s">
+        <v>73</v>
+      </c>
+      <c r="D256" t="s">
+        <v>35</v>
+      </c>
+      <c r="E256" t="s">
+        <v>74</v>
+      </c>
+      <c r="F256" t="s">
+        <v>78</v>
+      </c>
+      <c r="G256">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A257">
+        <v>1990</v>
+      </c>
+      <c r="B257" t="s">
+        <v>90</v>
+      </c>
+      <c r="C257" t="s">
+        <v>91</v>
+      </c>
+      <c r="D257" t="s">
+        <v>35</v>
+      </c>
+      <c r="E257" t="s">
+        <v>9</v>
+      </c>
+      <c r="F257" t="s">
+        <v>10</v>
+      </c>
+      <c r="G257">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A258">
+        <v>1990</v>
+      </c>
+      <c r="B258" t="s">
+        <v>48</v>
+      </c>
+      <c r="C258" t="s">
+        <v>49</v>
+      </c>
+      <c r="D258" t="s">
+        <v>35</v>
+      </c>
+      <c r="E258" t="s">
+        <v>37</v>
+      </c>
+      <c r="F258" t="s">
+        <v>22</v>
+      </c>
+      <c r="G258">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A259">
+        <v>1990</v>
+      </c>
+      <c r="B259" t="s">
+        <v>83</v>
+      </c>
+      <c r="C259" t="s">
+        <v>32</v>
+      </c>
+      <c r="D259" t="s">
+        <v>35</v>
+      </c>
+      <c r="E259" t="s">
+        <v>56</v>
+      </c>
+      <c r="F259" t="s">
+        <v>79</v>
+      </c>
+      <c r="G259">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A260">
+        <v>1990</v>
+      </c>
+      <c r="B260" t="s">
+        <v>39</v>
+      </c>
+      <c r="C260" t="s">
+        <v>70</v>
+      </c>
+      <c r="D260" t="s">
+        <v>35</v>
+      </c>
+      <c r="E260" t="s">
+        <v>13</v>
+      </c>
+      <c r="F260" t="s">
+        <v>14</v>
+      </c>
+      <c r="G260">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A261">
+        <v>1990</v>
+      </c>
+      <c r="B261" t="s">
+        <v>36</v>
+      </c>
+      <c r="C261" t="s">
+        <v>64</v>
+      </c>
+      <c r="D261" t="s">
+        <v>35</v>
+      </c>
+      <c r="E261" t="s">
+        <v>15</v>
+      </c>
+      <c r="F261" t="s">
+        <v>16</v>
+      </c>
+      <c r="G261">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A262">
+        <v>1990</v>
+      </c>
+      <c r="B262" t="s">
+        <v>84</v>
+      </c>
+      <c r="C262" t="s">
+        <v>85</v>
+      </c>
+      <c r="D262" t="s">
+        <v>35</v>
+      </c>
+      <c r="E262" t="s">
+        <v>17</v>
+      </c>
+      <c r="F262" t="s">
+        <v>75</v>
+      </c>
+      <c r="G262">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A263">
+        <v>1990</v>
+      </c>
+      <c r="B263" t="s">
+        <v>61</v>
+      </c>
+      <c r="C263" t="s">
+        <v>62</v>
+      </c>
+      <c r="D263" t="s">
+        <v>35</v>
+      </c>
+      <c r="E263" t="s">
+        <v>19</v>
+      </c>
+      <c r="F263" t="s">
+        <v>77</v>
+      </c>
+      <c r="G263">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A264">
+        <v>1990</v>
+      </c>
+      <c r="B264" t="s">
+        <v>46</v>
+      </c>
+      <c r="C264" t="s">
+        <v>64</v>
+      </c>
+      <c r="D264" t="s">
+        <v>35</v>
+      </c>
+      <c r="E264" t="s">
+        <v>71</v>
+      </c>
+      <c r="F264" t="s">
+        <v>76</v>
+      </c>
+      <c r="G264">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A265">
+        <v>1990</v>
+      </c>
+      <c r="B265" t="s">
+        <v>72</v>
+      </c>
+      <c r="C265" t="s">
+        <v>73</v>
+      </c>
+      <c r="D265" t="s">
+        <v>35</v>
+      </c>
+      <c r="E265" t="s">
+        <v>74</v>
+      </c>
+      <c r="F265" t="s">
+        <v>78</v>
+      </c>
+      <c r="G265">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A266">
+        <v>1989</v>
+      </c>
+      <c r="B266" t="s">
+        <v>90</v>
+      </c>
+      <c r="C266" t="s">
+        <v>91</v>
+      </c>
+      <c r="D266" t="s">
+        <v>35</v>
+      </c>
+      <c r="E266" t="s">
+        <v>37</v>
+      </c>
+      <c r="F266" t="s">
+        <v>10</v>
+      </c>
+      <c r="G266">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A267">
+        <v>1989</v>
+      </c>
+      <c r="B267" t="s">
+        <v>48</v>
+      </c>
+      <c r="C267" t="s">
+        <v>49</v>
+      </c>
+      <c r="D267" t="s">
+        <v>35</v>
+      </c>
+      <c r="E267" t="s">
+        <v>9</v>
+      </c>
+      <c r="F267" t="s">
+        <v>22</v>
+      </c>
+      <c r="G267">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A268">
+        <v>1989</v>
+      </c>
+      <c r="B268" t="s">
+        <v>83</v>
+      </c>
+      <c r="C268" t="s">
+        <v>32</v>
+      </c>
+      <c r="D268" t="s">
+        <v>35</v>
+      </c>
+      <c r="E268" t="s">
+        <v>56</v>
+      </c>
+      <c r="F268" t="s">
+        <v>79</v>
+      </c>
+      <c r="G268">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A269">
+        <v>1989</v>
+      </c>
+      <c r="B269" t="s">
+        <v>39</v>
+      </c>
+      <c r="C269" t="s">
+        <v>70</v>
+      </c>
+      <c r="D269" t="s">
+        <v>35</v>
+      </c>
+      <c r="E269" t="s">
+        <v>13</v>
+      </c>
+      <c r="F269" t="s">
+        <v>14</v>
+      </c>
+      <c r="G269">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A270">
+        <v>1989</v>
+      </c>
+      <c r="B270" t="s">
+        <v>36</v>
+      </c>
+      <c r="C270" t="s">
+        <v>64</v>
+      </c>
+      <c r="D270" t="s">
+        <v>35</v>
+      </c>
+      <c r="E270" t="s">
+        <v>15</v>
+      </c>
+      <c r="F270" t="s">
+        <v>16</v>
+      </c>
+      <c r="G270">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A271">
+        <v>1989</v>
+      </c>
+      <c r="B271" t="s">
+        <v>84</v>
+      </c>
+      <c r="C271" t="s">
+        <v>85</v>
+      </c>
+      <c r="D271" t="s">
+        <v>35</v>
+      </c>
+      <c r="E271" t="s">
+        <v>17</v>
+      </c>
+      <c r="F271" t="s">
+        <v>75</v>
+      </c>
+      <c r="G271">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A272">
+        <v>1989</v>
+      </c>
+      <c r="B272" t="s">
+        <v>86</v>
+      </c>
+      <c r="C272" t="s">
+        <v>60</v>
+      </c>
+      <c r="D272" t="s">
+        <v>35</v>
+      </c>
+      <c r="E272" t="s">
+        <v>19</v>
+      </c>
+      <c r="F272" t="s">
+        <v>77</v>
+      </c>
+      <c r="G272">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A273">
+        <v>1989</v>
+      </c>
+      <c r="B273" t="s">
+        <v>46</v>
+      </c>
+      <c r="C273" t="s">
+        <v>64</v>
+      </c>
+      <c r="D273" t="s">
+        <v>35</v>
+      </c>
+      <c r="E273" t="s">
+        <v>71</v>
+      </c>
+      <c r="F273" t="s">
+        <v>76</v>
+      </c>
+      <c r="G273">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A274">
+        <v>1989</v>
+      </c>
+      <c r="B274" t="s">
+        <v>87</v>
+      </c>
+      <c r="C274" t="s">
+        <v>32</v>
+      </c>
+      <c r="D274" t="s">
+        <v>35</v>
+      </c>
+      <c r="E274" t="s">
+        <v>74</v>
+      </c>
+      <c r="F274" t="s">
+        <v>78</v>
+      </c>
+      <c r="G274">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A275">
+        <v>1988</v>
+      </c>
+      <c r="B275" t="s">
+        <v>90</v>
+      </c>
+      <c r="C275" t="s">
+        <v>91</v>
+      </c>
+      <c r="D275" t="s">
+        <v>35</v>
+      </c>
+      <c r="E275" t="s">
+        <v>37</v>
+      </c>
+      <c r="F275" t="s">
+        <v>10</v>
+      </c>
+      <c r="G275">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A276">
+        <v>1988</v>
+      </c>
+      <c r="B276" t="s">
+        <v>48</v>
+      </c>
+      <c r="C276" t="s">
+        <v>49</v>
+      </c>
+      <c r="D276" t="s">
+        <v>35</v>
+      </c>
+      <c r="E276" t="s">
+        <v>9</v>
+      </c>
+      <c r="F276" t="s">
+        <v>22</v>
+      </c>
+      <c r="G276">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A277">
+        <v>1988</v>
+      </c>
+      <c r="B277" t="s">
+        <v>83</v>
+      </c>
+      <c r="C277" t="s">
+        <v>32</v>
+      </c>
+      <c r="D277" t="s">
+        <v>35</v>
+      </c>
+      <c r="E277" t="s">
+        <v>56</v>
+      </c>
+      <c r="F277" t="s">
+        <v>79</v>
+      </c>
+      <c r="G277">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A278">
+        <v>1988</v>
+      </c>
+      <c r="B278" t="s">
+        <v>39</v>
+      </c>
+      <c r="C278" t="s">
+        <v>70</v>
+      </c>
+      <c r="D278" t="s">
+        <v>35</v>
+      </c>
+      <c r="E278" t="s">
+        <v>13</v>
+      </c>
+      <c r="F278" t="s">
+        <v>14</v>
+      </c>
+      <c r="G278">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A279">
+        <v>1988</v>
+      </c>
+      <c r="B279" t="s">
+        <v>36</v>
+      </c>
+      <c r="C279" t="s">
+        <v>64</v>
+      </c>
+      <c r="D279" t="s">
+        <v>35</v>
+      </c>
+      <c r="E279" t="s">
+        <v>15</v>
+      </c>
+      <c r="F279" t="s">
+        <v>16</v>
+      </c>
+      <c r="G279">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A280">
+        <v>1988</v>
+      </c>
+      <c r="B280" t="s">
+        <v>84</v>
+      </c>
+      <c r="C280" t="s">
+        <v>85</v>
+      </c>
+      <c r="D280" t="s">
+        <v>35</v>
+      </c>
+      <c r="E280" t="s">
+        <v>17</v>
+      </c>
+      <c r="F280" t="s">
+        <v>75</v>
+      </c>
+      <c r="G280">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A281">
+        <v>1988</v>
+      </c>
+      <c r="B281" t="s">
+        <v>86</v>
+      </c>
+      <c r="C281" t="s">
+        <v>60</v>
+      </c>
+      <c r="D281" t="s">
+        <v>35</v>
+      </c>
+      <c r="E281" t="s">
+        <v>19</v>
+      </c>
+      <c r="F281" t="s">
+        <v>77</v>
+      </c>
+      <c r="G281">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A282">
+        <v>1988</v>
+      </c>
+      <c r="B282" t="s">
+        <v>46</v>
+      </c>
+      <c r="C282" t="s">
+        <v>64</v>
+      </c>
+      <c r="D282" t="s">
+        <v>35</v>
+      </c>
+      <c r="E282" t="s">
+        <v>71</v>
+      </c>
+      <c r="F282" t="s">
+        <v>76</v>
+      </c>
+      <c r="G282">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A283">
+        <v>1988</v>
+      </c>
+      <c r="B283" t="s">
+        <v>87</v>
+      </c>
+      <c r="C283" t="s">
+        <v>32</v>
+      </c>
+      <c r="D283" t="s">
+        <v>35</v>
+      </c>
+      <c r="E283" t="s">
+        <v>74</v>
+      </c>
+      <c r="F283" t="s">
+        <v>78</v>
+      </c>
+      <c r="G283">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A284">
+        <v>1987</v>
+      </c>
+      <c r="B284" t="s">
+        <v>90</v>
+      </c>
+      <c r="C284" t="s">
+        <v>91</v>
+      </c>
+      <c r="D284" t="s">
+        <v>35</v>
+      </c>
+      <c r="E284" t="s">
+        <v>9</v>
+      </c>
+      <c r="F284" t="s">
+        <v>10</v>
+      </c>
+      <c r="G284">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A285">
+        <v>1987</v>
+      </c>
+      <c r="B285" t="s">
+        <v>48</v>
+      </c>
+      <c r="C285" t="s">
+        <v>49</v>
+      </c>
+      <c r="D285" t="s">
+        <v>35</v>
+      </c>
+      <c r="E285" t="s">
+        <v>37</v>
+      </c>
+      <c r="F285" t="s">
+        <v>22</v>
+      </c>
+      <c r="G285">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A286">
+        <v>1987</v>
+      </c>
+      <c r="B286" t="s">
+        <v>83</v>
+      </c>
+      <c r="C286" t="s">
+        <v>32</v>
+      </c>
+      <c r="D286" t="s">
+        <v>35</v>
+      </c>
+      <c r="E286" t="s">
+        <v>56</v>
+      </c>
+      <c r="F286" t="s">
+        <v>79</v>
+      </c>
+      <c r="G286">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A287">
+        <v>1987</v>
+      </c>
+      <c r="B287" t="s">
+        <v>26</v>
+      </c>
+      <c r="C287" t="s">
+        <v>88</v>
+      </c>
+      <c r="D287" t="s">
+        <v>35</v>
+      </c>
+      <c r="E287" t="s">
+        <v>13</v>
+      </c>
+      <c r="F287" t="s">
+        <v>14</v>
+      </c>
+      <c r="G287">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A288">
+        <v>1987</v>
+      </c>
+      <c r="B288" t="s">
+        <v>36</v>
+      </c>
+      <c r="C288" t="s">
+        <v>64</v>
+      </c>
+      <c r="D288" t="s">
+        <v>35</v>
+      </c>
+      <c r="E288" t="s">
+        <v>15</v>
+      </c>
+      <c r="F288" t="s">
+        <v>16</v>
+      </c>
+      <c r="G288">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A289">
+        <v>1987</v>
+      </c>
+      <c r="B289" t="s">
+        <v>84</v>
+      </c>
+      <c r="C289" t="s">
+        <v>85</v>
+      </c>
+      <c r="D289" t="s">
+        <v>35</v>
+      </c>
+      <c r="E289" t="s">
+        <v>17</v>
+      </c>
+      <c r="F289" t="s">
+        <v>75</v>
+      </c>
+      <c r="G289">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A290">
+        <v>1987</v>
+      </c>
+      <c r="B290" t="s">
+        <v>86</v>
+      </c>
+      <c r="C290" t="s">
+        <v>60</v>
+      </c>
+      <c r="D290" t="s">
+        <v>35</v>
+      </c>
+      <c r="E290" t="s">
+        <v>19</v>
+      </c>
+      <c r="F290" t="s">
+        <v>77</v>
+      </c>
+      <c r="G290">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A291">
+        <v>1987</v>
+      </c>
+      <c r="B291" t="s">
+        <v>46</v>
+      </c>
+      <c r="C291" t="s">
+        <v>64</v>
+      </c>
+      <c r="D291" t="s">
+        <v>35</v>
+      </c>
+      <c r="E291" t="s">
+        <v>71</v>
+      </c>
+      <c r="F291" t="s">
+        <v>76</v>
+      </c>
+      <c r="G291">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A292">
+        <v>1987</v>
+      </c>
+      <c r="B292" t="s">
+        <v>87</v>
+      </c>
+      <c r="C292" t="s">
+        <v>32</v>
+      </c>
+      <c r="D292" t="s">
+        <v>35</v>
+      </c>
+      <c r="E292" t="s">
+        <v>74</v>
+      </c>
+      <c r="F292" t="s">
+        <v>78</v>
+      </c>
+      <c r="G292">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A293">
+        <v>1986</v>
+      </c>
+      <c r="B293" t="s">
+        <v>90</v>
+      </c>
+      <c r="C293" t="s">
+        <v>91</v>
+      </c>
+      <c r="D293" t="s">
+        <v>35</v>
+      </c>
+      <c r="E293" t="s">
+        <v>9</v>
+      </c>
+      <c r="F293" t="s">
+        <v>10</v>
+      </c>
+      <c r="G293">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A294">
+        <v>1986</v>
+      </c>
+      <c r="B294" t="s">
+        <v>48</v>
+      </c>
+      <c r="C294" t="s">
+        <v>49</v>
+      </c>
+      <c r="D294" t="s">
+        <v>35</v>
+      </c>
+      <c r="E294" t="s">
+        <v>37</v>
+      </c>
+      <c r="F294" t="s">
+        <v>22</v>
+      </c>
+      <c r="G294">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A295">
+        <v>1986</v>
+      </c>
+      <c r="B295" t="s">
+        <v>83</v>
+      </c>
+      <c r="C295" t="s">
+        <v>32</v>
+      </c>
+      <c r="D295" t="s">
+        <v>35</v>
+      </c>
+      <c r="E295" t="s">
+        <v>56</v>
+      </c>
+      <c r="F295" t="s">
+        <v>79</v>
+      </c>
+      <c r="G295">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A296">
+        <v>1986</v>
+      </c>
+      <c r="B296" t="s">
+        <v>26</v>
+      </c>
+      <c r="C296" t="s">
+        <v>88</v>
+      </c>
+      <c r="D296" t="s">
+        <v>35</v>
+      </c>
+      <c r="E296" t="s">
+        <v>13</v>
+      </c>
+      <c r="F296" t="s">
+        <v>14</v>
+      </c>
+      <c r="G296">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A297">
+        <v>1986</v>
+      </c>
+      <c r="B297" t="s">
+        <v>36</v>
+      </c>
+      <c r="C297" t="s">
+        <v>64</v>
+      </c>
+      <c r="D297" t="s">
+        <v>35</v>
+      </c>
+      <c r="E297" t="s">
+        <v>15</v>
+      </c>
+      <c r="F297" t="s">
+        <v>81</v>
+      </c>
+      <c r="G297">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A298">
+        <v>1986</v>
+      </c>
+      <c r="B298" t="s">
+        <v>84</v>
+      </c>
+      <c r="C298" t="s">
+        <v>85</v>
+      </c>
+      <c r="D298" t="s">
+        <v>35</v>
+      </c>
+      <c r="E298" t="s">
+        <v>17</v>
+      </c>
+      <c r="F298" t="s">
+        <v>75</v>
+      </c>
+      <c r="G298">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A299">
+        <v>1986</v>
+      </c>
+      <c r="B299" t="s">
+        <v>86</v>
+      </c>
+      <c r="C299" t="s">
+        <v>60</v>
+      </c>
+      <c r="D299" t="s">
+        <v>35</v>
+      </c>
+      <c r="E299" t="s">
+        <v>19</v>
+      </c>
+      <c r="F299" t="s">
+        <v>77</v>
+      </c>
+      <c r="G299">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A300">
+        <v>1986</v>
+      </c>
+      <c r="B300" t="s">
+        <v>83</v>
+      </c>
+      <c r="C300" t="s">
+        <v>64</v>
+      </c>
+      <c r="D300" t="s">
+        <v>35</v>
+      </c>
+      <c r="E300" t="s">
+        <v>71</v>
+      </c>
+      <c r="F300" t="s">
+        <v>76</v>
+      </c>
+      <c r="G300">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A301">
+        <v>1986</v>
+      </c>
+      <c r="B301" t="s">
+        <v>87</v>
+      </c>
+      <c r="C301" t="s">
+        <v>32</v>
+      </c>
+      <c r="D301" t="s">
+        <v>35</v>
+      </c>
+      <c r="E301" t="s">
+        <v>74</v>
+      </c>
+      <c r="F301" t="s">
+        <v>78</v>
+      </c>
+      <c r="G301">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="302" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A302">
+        <v>1985</v>
+      </c>
+      <c r="B302" t="s">
+        <v>90</v>
+      </c>
+      <c r="C302" t="s">
+        <v>91</v>
+      </c>
+      <c r="D302" t="s">
+        <v>35</v>
+      </c>
+      <c r="E302" t="s">
+        <v>37</v>
+      </c>
+      <c r="F302" t="s">
+        <v>10</v>
+      </c>
+      <c r="G302">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="303" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A303">
+        <v>1985</v>
+      </c>
+      <c r="B303" t="s">
+        <v>48</v>
+      </c>
+      <c r="C303" t="s">
+        <v>49</v>
+      </c>
+      <c r="D303" t="s">
+        <v>35</v>
+      </c>
+      <c r="E303" t="s">
+        <v>9</v>
+      </c>
+      <c r="F303" t="s">
+        <v>22</v>
+      </c>
+      <c r="G303">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A304">
+        <v>1985</v>
+      </c>
+      <c r="B304" t="s">
+        <v>46</v>
+      </c>
+      <c r="C304" t="s">
+        <v>62</v>
+      </c>
+      <c r="D304" t="s">
+        <v>35</v>
+      </c>
+      <c r="E304" t="s">
+        <v>56</v>
+      </c>
+      <c r="F304" t="s">
+        <v>79</v>
+      </c>
+      <c r="G304">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A305">
+        <v>1985</v>
+      </c>
+      <c r="B305" t="s">
+        <v>26</v>
+      </c>
+      <c r="C305" t="s">
+        <v>88</v>
+      </c>
+      <c r="D305" t="s">
+        <v>35</v>
+      </c>
+      <c r="E305" t="s">
+        <v>13</v>
+      </c>
+      <c r="F305" t="s">
+        <v>14</v>
+      </c>
+      <c r="G305">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A306">
+        <v>1985</v>
+      </c>
+      <c r="B306" t="s">
+        <v>36</v>
+      </c>
+      <c r="C306" t="s">
+        <v>64</v>
+      </c>
+      <c r="D306" t="s">
+        <v>35</v>
+      </c>
+      <c r="E306" t="s">
+        <v>15</v>
+      </c>
+      <c r="F306" t="s">
+        <v>16</v>
+      </c>
+      <c r="G306">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A307">
+        <v>1985</v>
+      </c>
+      <c r="B307" t="s">
+        <v>84</v>
+      </c>
+      <c r="C307" t="s">
+        <v>85</v>
+      </c>
+      <c r="D307" t="s">
+        <v>35</v>
+      </c>
+      <c r="E307" t="s">
+        <v>17</v>
+      </c>
+      <c r="F307" t="s">
+        <v>75</v>
+      </c>
+      <c r="G307">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A308">
+        <v>1985</v>
+      </c>
+      <c r="B308" t="s">
+        <v>86</v>
+      </c>
+      <c r="C308" t="s">
+        <v>60</v>
+      </c>
+      <c r="D308" t="s">
+        <v>35</v>
+      </c>
+      <c r="E308" t="s">
+        <v>19</v>
+      </c>
+      <c r="F308" t="s">
+        <v>77</v>
+      </c>
+      <c r="G308">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A309">
+        <v>1985</v>
+      </c>
+      <c r="B309" t="s">
+        <v>83</v>
+      </c>
+      <c r="C309" t="s">
+        <v>64</v>
+      </c>
+      <c r="D309" t="s">
+        <v>35</v>
+      </c>
+      <c r="E309" t="s">
+        <v>71</v>
+      </c>
+      <c r="F309" t="s">
+        <v>76</v>
+      </c>
+      <c r="G309">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="310" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A310">
+        <v>1985</v>
+      </c>
+      <c r="B310" t="s">
+        <v>87</v>
+      </c>
+      <c r="C310" t="s">
+        <v>32</v>
+      </c>
+      <c r="D310" t="s">
+        <v>35</v>
+      </c>
+      <c r="E310" t="s">
+        <v>74</v>
+      </c>
+      <c r="F310" t="s">
+        <v>78</v>
+      </c>
+      <c r="G310">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="311" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A311">
+        <v>1984</v>
+      </c>
+      <c r="B311" t="s">
+        <v>92</v>
+      </c>
+      <c r="C311" t="s">
+        <v>93</v>
+      </c>
+      <c r="D311" t="s">
+        <v>35</v>
+      </c>
+      <c r="E311" t="s">
+        <v>37</v>
+      </c>
+      <c r="F311" t="s">
+        <v>10</v>
+      </c>
+      <c r="G311">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="312" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A312">
+        <v>1984</v>
+      </c>
+      <c r="B312" t="s">
+        <v>48</v>
+      </c>
+      <c r="C312" t="s">
+        <v>49</v>
+      </c>
+      <c r="D312" t="s">
+        <v>35</v>
+      </c>
+      <c r="E312" t="s">
+        <v>9</v>
+      </c>
+      <c r="F312" t="s">
+        <v>22</v>
+      </c>
+      <c r="G312">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="313" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A313">
+        <v>1984</v>
+      </c>
+      <c r="B313" t="s">
+        <v>46</v>
+      </c>
+      <c r="C313" t="s">
+        <v>62</v>
+      </c>
+      <c r="D313" t="s">
+        <v>35</v>
+      </c>
+      <c r="E313" t="s">
+        <v>56</v>
+      </c>
+      <c r="F313" t="s">
+        <v>79</v>
+      </c>
+      <c r="G313">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A314">
+        <v>1984</v>
+      </c>
+      <c r="B314" t="s">
+        <v>26</v>
+      </c>
+      <c r="C314" t="s">
+        <v>88</v>
+      </c>
+      <c r="D314" t="s">
+        <v>35</v>
+      </c>
+      <c r="E314" t="s">
+        <v>13</v>
+      </c>
+      <c r="F314" t="s">
+        <v>14</v>
+      </c>
+      <c r="G314">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="315" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A315">
+        <v>1984</v>
+      </c>
+      <c r="B315" t="s">
+        <v>36</v>
+      </c>
+      <c r="C315" t="s">
+        <v>64</v>
+      </c>
+      <c r="D315" t="s">
+        <v>35</v>
+      </c>
+      <c r="E315" t="s">
+        <v>15</v>
+      </c>
+      <c r="F315" t="s">
+        <v>16</v>
+      </c>
+      <c r="G315">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="316" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A316">
+        <v>1984</v>
+      </c>
+      <c r="B316" t="s">
+        <v>84</v>
+      </c>
+      <c r="C316" t="s">
+        <v>85</v>
+      </c>
+      <c r="D316" t="s">
+        <v>35</v>
+      </c>
+      <c r="E316" t="s">
+        <v>17</v>
+      </c>
+      <c r="F316" t="s">
+        <v>75</v>
+      </c>
+      <c r="G316">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="317" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A317">
+        <v>1984</v>
+      </c>
+      <c r="B317" t="s">
+        <v>86</v>
+      </c>
+      <c r="C317" t="s">
+        <v>60</v>
+      </c>
+      <c r="D317" t="s">
+        <v>35</v>
+      </c>
+      <c r="E317" t="s">
+        <v>19</v>
+      </c>
+      <c r="F317" t="s">
+        <v>77</v>
+      </c>
+      <c r="G317">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="318" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A318">
+        <v>1984</v>
+      </c>
+      <c r="B318" t="s">
+        <v>83</v>
+      </c>
+      <c r="C318" t="s">
+        <v>64</v>
+      </c>
+      <c r="D318" t="s">
+        <v>35</v>
+      </c>
+      <c r="E318" t="s">
+        <v>71</v>
+      </c>
+      <c r="F318" t="s">
+        <v>76</v>
+      </c>
+      <c r="G318">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="319" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A319">
+        <v>1984</v>
+      </c>
+      <c r="B319" t="s">
+        <v>87</v>
+      </c>
+      <c r="C319" t="s">
+        <v>32</v>
+      </c>
+      <c r="D319" t="s">
+        <v>35</v>
+      </c>
+      <c r="E319" t="s">
+        <v>74</v>
+      </c>
+      <c r="F319" t="s">
+        <v>78</v>
+      </c>
+      <c r="G319">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="320" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A320" s="1">
+        <v>1983</v>
+      </c>
+      <c r="B320" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C320" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D320" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E320" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F320" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G320" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="321" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A321" s="1">
+        <v>1983</v>
+      </c>
+      <c r="B321" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C321" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D321" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E321" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F321" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G321" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="322" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A322" s="1">
+        <v>1983</v>
+      </c>
+      <c r="B322" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C322" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D322" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E322" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F322" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G322" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="323" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A323" s="1">
+        <v>1983</v>
+      </c>
+      <c r="B323" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C323" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D323" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E323" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F323" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G323" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="324" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A324" s="1">
+        <v>1983</v>
+      </c>
+      <c r="B324" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C324" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D324" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E324" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F324" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G324" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="325" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A325" s="1">
+        <v>1983</v>
+      </c>
+      <c r="B325" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C325" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D325" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E325" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F325" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G325" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="326" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A326" s="1">
+        <v>1983</v>
+      </c>
+      <c r="B326" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C326" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D326" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E326" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F326" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G326" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="327" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A327" s="1">
+        <v>1983</v>
+      </c>
+      <c r="B327" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C327" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D327" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E327" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F327" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G327" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="328" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A328" s="1">
+        <v>1982</v>
+      </c>
+      <c r="B328" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C328" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D328" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E328" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F328" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G328" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="329" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A329" s="1">
+        <v>1982</v>
+      </c>
+      <c r="B329" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C329" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D329" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E329" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F329" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G329" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="330" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A330" s="1">
+        <v>1982</v>
+      </c>
+      <c r="B330" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C330" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D330" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E330" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F330" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G330" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="331" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A331" s="1">
+        <v>1982</v>
+      </c>
+      <c r="B331" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C331" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D331" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E331" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F331" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G331" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="332" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A332" s="1">
+        <v>1982</v>
+      </c>
+      <c r="B332" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C332" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D332" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E332" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F332" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G332" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="333" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A333" s="1">
+        <v>1982</v>
+      </c>
+      <c r="B333" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C333" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D333" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E333" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F333" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G333" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="334" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A334" s="1">
+        <v>1982</v>
+      </c>
+      <c r="B334" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C334" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D334" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E334" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F334" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G334" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="335" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A335" s="1">
+        <v>1982</v>
+      </c>
+      <c r="B335" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C335" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D335" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E335" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F335" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G335" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="336" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A336" s="1">
+        <v>1981</v>
+      </c>
+      <c r="B336" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C336" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D336" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E336" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F336" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G336" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="337" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A337" s="1">
+        <v>1981</v>
+      </c>
+      <c r="B337" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C337" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D337" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E337" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F337" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G337" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="338" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A338" s="1">
+        <v>1981</v>
+      </c>
+      <c r="B338" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C338" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D338" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E338" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F338" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G338" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="339" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A339" s="1">
+        <v>1981</v>
+      </c>
+      <c r="B339" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C339" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D339" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E339" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F339" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G339" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="340" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A340" s="1">
+        <v>1981</v>
+      </c>
+      <c r="B340" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C340" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D340" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E340" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F340" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G340" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="341" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A341" s="1">
+        <v>1981</v>
+      </c>
+      <c r="B341" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C341" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D341" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E341" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F341" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G341" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="342" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A342" s="1">
+        <v>1981</v>
+      </c>
+      <c r="B342" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C342" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D342" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E342" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F342" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G342" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="343" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A343" s="1">
+        <v>1980</v>
+      </c>
+      <c r="B343" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C343" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D343" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E343" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F343" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G343" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="344" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A344" s="1">
+        <v>1980</v>
+      </c>
+      <c r="B344" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C344" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D344" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E344" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F344" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G344" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="345" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A345" s="1">
+        <v>1980</v>
+      </c>
+      <c r="B345" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C345" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D345" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E345" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F345" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G345" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="346" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A346" s="1">
+        <v>1980</v>
+      </c>
+      <c r="B346" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C346" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D346" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E346" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F346" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G346" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="347" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A347" s="1">
+        <v>1980</v>
+      </c>
+      <c r="B347" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C347" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D347" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E347" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F347" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G347" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="348" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A348" s="1">
+        <v>1980</v>
+      </c>
+      <c r="B348" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C348" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D348" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E348" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F348" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G348" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="349" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A349" s="1">
+        <v>1980</v>
+      </c>
+      <c r="B349" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C349" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D349" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E349" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F349" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G349" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="350" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A350" s="1">
+        <v>1979</v>
+      </c>
+      <c r="B350" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C350" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D350" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E350" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F350" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G350" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="351" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A351" s="1">
+        <v>1979</v>
+      </c>
+      <c r="B351" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C351" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D351" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E351" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F351" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G351" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="352" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A352" s="1">
+        <v>1979</v>
+      </c>
+      <c r="B352" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C352" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D352" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E352" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F352" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G352" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="353" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A353" s="1">
+        <v>1979</v>
+      </c>
+      <c r="B353" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C353" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D353" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E353" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F353" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G353" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="354" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A354" s="1">
+        <v>1978</v>
+      </c>
+      <c r="B354" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C354" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D354" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E354" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F354" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G354" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="355" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A355" s="1">
+        <v>1978</v>
+      </c>
+      <c r="B355" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C355" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D355" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E355" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F355" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G355" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="356" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A356" s="1">
+        <v>1978</v>
+      </c>
+      <c r="B356" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C356" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D356" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E356" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F356" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G356" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="357" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A357" s="1">
+        <v>1977</v>
+      </c>
+      <c r="B357" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C357" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D357" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E357" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F357" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G357" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="358" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A358" s="1">
+        <v>1977</v>
+      </c>
+      <c r="B358" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C358" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D358" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E358" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F358" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G358" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="359" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A359" s="1">
+        <v>1976</v>
+      </c>
+      <c r="B359" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C359" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D359" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E359" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F359" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G359" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="360" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A360" s="1">
+        <v>1976</v>
+      </c>
+      <c r="B360" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C360" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D360" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E360" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F360" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G360" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="361" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A361" s="1">
+        <v>1975</v>
+      </c>
+      <c r="B361" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C361" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D361" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E361" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F361" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G361" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="362" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A362" s="1">
+        <v>1974</v>
+      </c>
+      <c r="B362" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C362" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D362" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E362" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F362" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G362" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="363" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A363" s="1">
+        <v>1973</v>
+      </c>
+      <c r="B363" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C363" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D363" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E363" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F363" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G363" s="1">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G1" xr:uid="{2FB2D094-259F-4BDA-9CCC-AC85399FAC35}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G363">
+      <sortCondition descending="1" ref="A1"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
